--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_45.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3056054.364459014</v>
+        <v>3049187.371510357</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10041900.99034355</v>
+        <v>10041900.99034356</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10041900.99034355</v>
+        <v>10041900.99034356</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162898723</v>
+        <v>286.4107162899563</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162898723</v>
+        <v>286.4107162899563</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,25 +781,25 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>333.9365645502421</v>
       </c>
       <c r="S3" t="n">
-        <v>66.5639999646113</v>
+        <v>385</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>275.6723376976487</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X3" t="n">
-        <v>385</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -857,7 +857,7 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q4" t="n">
-        <v>325.839266425598</v>
+        <v>324.2480957795422</v>
       </c>
       <c r="R4" t="n">
         <v>326.6021279811511</v>
@@ -894,7 +894,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>78.1807696284084</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111.6257119379035</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>308.4311513056531</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172657</v>
+        <v>21.95645751172477</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1450,7 +1450,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>332.1680871864211</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1684,7 +1684,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1729,16 +1729,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178217</v>
       </c>
       <c r="S15" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T15" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U15" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V15" t="n">
         <v>64.51066719152016</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>144.8481678023229</v>
@@ -1927,16 +1927,16 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2161,7 +2161,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T21" t="n">
         <v>55.35776521751382</v>
@@ -2221,7 +2221,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>49.39139276613435</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>242.2818334606677</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,13 +2440,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U24" t="n">
         <v>50.21035976018675</v>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176916</v>
       </c>
       <c r="C27" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2644,10 +2644,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>80.50967533902147</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S29" t="n">
         <v>144.8481678023229</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S30" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T30" t="n">
         <v>55.35776521751382</v>
@@ -2935,7 +2935,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -3039,13 +3039,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3148,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>259.9515598178217</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S33" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T33" t="n">
         <v>55.35776521751382</v>
@@ -3276,7 +3276,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>230.1079332804206</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3580,7 +3580,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>206.6512890796133</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H42" t="n">
         <v>332.1680871864211</v>
@@ -3865,7 +3865,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>197.0736753036327</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>97.2343191717691</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>284.2120239427945</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4120,7 +4120,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4297,46 +4297,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M2" t="n">
         <v>411.95</v>
       </c>
-      <c r="K2" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="L2" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="M2" t="n">
-        <v>793.1</v>
-      </c>
       <c r="N2" t="n">
-        <v>1158.85</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1540</v>
+        <v>1174.25</v>
       </c>
       <c r="P2" t="n">
         <v>1540</v>
@@ -4345,28 +4345,28 @@
         <v>1540</v>
       </c>
       <c r="R2" t="n">
-        <v>1511.00384708544</v>
+        <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="C3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="D3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="E3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="F3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="G3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4424,28 +4424,28 @@
         <v>1186.232420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.471008962092</v>
+        <v>848.922759206675</v>
       </c>
       <c r="S3" t="n">
-        <v>970.2346453614745</v>
+        <v>460.0338703177861</v>
       </c>
       <c r="T3" t="n">
-        <v>964.8227613033797</v>
+        <v>454.6219862596914</v>
       </c>
       <c r="U3" t="n">
-        <v>686.365854538078</v>
+        <v>454.4095016534421</v>
       </c>
       <c r="V3" t="n">
-        <v>671.7086149506839</v>
+        <v>439.752262066048</v>
       </c>
       <c r="W3" t="n">
-        <v>639.0084705973218</v>
+        <v>50.86337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>490.0382863254434</v>
+        <v>378.6289856464112</v>
       </c>
       <c r="C4" t="n">
-        <v>616.0402921438792</v>
+        <v>504.6309914648469</v>
       </c>
       <c r="D4" t="n">
-        <v>616.0402921438792</v>
+        <v>617.950135589847</v>
       </c>
       <c r="E4" t="n">
-        <v>616.0402921438792</v>
+        <v>735.7790398012601</v>
       </c>
       <c r="F4" t="n">
-        <v>740.4012647358147</v>
+        <v>860.1400123931955</v>
       </c>
       <c r="G4" t="n">
-        <v>788.2667952520683</v>
+        <v>1013.546578280081</v>
       </c>
       <c r="H4" t="n">
-        <v>957.7833804114658</v>
+        <v>1183.063163439478</v>
       </c>
       <c r="I4" t="n">
-        <v>1178.916259347549</v>
+        <v>1404.196042375561</v>
       </c>
       <c r="J4" t="n">
         <v>1540</v>
@@ -4485,19 +4485,19 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
         <v>360.7011393749001</v>
@@ -4524,7 +4524,7 @@
         <v>266.8716479801191</v>
       </c>
       <c r="Y4" t="n">
-        <v>378.2809486591513</v>
+        <v>266.8716479801191</v>
       </c>
     </row>
     <row r="5">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C5" t="n">
         <v>62.47586368209485</v>
@@ -4561,22 +4561,22 @@
         <v>30.8</v>
       </c>
       <c r="K5" t="n">
-        <v>396.5499999999959</v>
+        <v>30.8</v>
       </c>
       <c r="L5" t="n">
-        <v>396.5499999999959</v>
+        <v>30.8</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999978</v>
+        <v>30.8</v>
       </c>
       <c r="N5" t="n">
-        <v>777.6999999999978</v>
+        <v>396.55</v>
       </c>
       <c r="O5" t="n">
-        <v>777.6999999999978</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1158.849999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4585,25 +4585,25 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>664.2482646830374</v>
+        <v>229.621392885946</v>
       </c>
       <c r="C7" t="n">
-        <v>790.2502705014732</v>
+        <v>229.621392885946</v>
       </c>
       <c r="D7" t="n">
-        <v>790.2502705014732</v>
+        <v>342.9405370109461</v>
       </c>
       <c r="E7" t="n">
-        <v>908.0791747128862</v>
+        <v>460.7694412223591</v>
       </c>
       <c r="F7" t="n">
-        <v>908.0791747128862</v>
+        <v>585.1304138142946</v>
       </c>
       <c r="G7" t="n">
-        <v>1061.485740599772</v>
+        <v>738.5369797011798</v>
       </c>
       <c r="H7" t="n">
-        <v>1231.002325759169</v>
+        <v>908.0535648605774</v>
       </c>
       <c r="I7" t="n">
-        <v>1452.135204695252</v>
+        <v>1129.18644379666</v>
       </c>
       <c r="J7" t="n">
-        <v>1540</v>
+        <v>1490.270184449112</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M7" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N7" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O7" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P7" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q7" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
@@ -4746,22 +4746,22 @@
         <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>218.8756791588049</v>
+        <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>465.4268717970915</v>
+        <v>30.8</v>
       </c>
       <c r="V7" t="n">
-        <v>664.2482646830374</v>
+        <v>229.621392885946</v>
       </c>
       <c r="W7" t="n">
-        <v>664.2482646830374</v>
+        <v>229.621392885946</v>
       </c>
       <c r="X7" t="n">
-        <v>664.2482646830374</v>
+        <v>229.621392885946</v>
       </c>
       <c r="Y7" t="n">
-        <v>664.2482646830374</v>
+        <v>229.621392885946</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
@@ -4804,43 +4804,43 @@
         <v>30.8</v>
       </c>
       <c r="M8" t="n">
-        <v>411.9500000000028</v>
+        <v>411.95</v>
       </c>
       <c r="N8" t="n">
-        <v>793.1000000000042</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1158.849999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="P8" t="n">
-        <v>1158.849999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
       </c>
       <c r="R8" t="n">
-        <v>1511.00384708544</v>
+        <v>1540</v>
       </c>
       <c r="S8" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>395.5473863086054</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E9" t="n">
-        <v>30.8</v>
+        <v>585.6429020987573</v>
       </c>
       <c r="F9" t="n">
-        <v>30.8</v>
+        <v>585.6429020987573</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>585.6429020987573</v>
       </c>
       <c r="H9" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I9" t="n">
         <v>30.8</v>
@@ -4919,7 +4919,7 @@
         <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>508.3006306903261</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>577.3895764229453</v>
+        <v>514.4329432708513</v>
       </c>
       <c r="C10" t="n">
-        <v>703.3915822413811</v>
+        <v>640.4349490892871</v>
       </c>
       <c r="D10" t="n">
-        <v>797.3163553123854</v>
+        <v>753.7540932142872</v>
       </c>
       <c r="E10" t="n">
-        <v>915.1452595237985</v>
+        <v>871.5829974257002</v>
       </c>
       <c r="F10" t="n">
-        <v>915.1452595237985</v>
+        <v>995.9439700176357</v>
       </c>
       <c r="G10" t="n">
-        <v>1068.551825410684</v>
+        <v>1149.350535904521</v>
       </c>
       <c r="H10" t="n">
-        <v>1068.551825410684</v>
+        <v>1318.867121063919</v>
       </c>
       <c r="I10" t="n">
-        <v>1068.551825410684</v>
+        <v>1540.000000000002</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063135</v>
+        <v>1540.000000000002</v>
       </c>
       <c r="K10" t="n">
-        <v>1540.000000000003</v>
+        <v>1540.000000000002</v>
       </c>
       <c r="L10" t="n">
         <v>1517.821760089168</v>
@@ -4980,25 +4980,25 @@
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="U10" t="n">
-        <v>314.6014477324597</v>
+        <v>30.8</v>
       </c>
       <c r="V10" t="n">
-        <v>314.6014477324597</v>
+        <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>314.6014477324597</v>
+        <v>140.2355139013334</v>
       </c>
       <c r="X10" t="n">
-        <v>465.6322387566532</v>
+        <v>291.2663049255269</v>
       </c>
       <c r="Y10" t="n">
-        <v>465.6322387566532</v>
+        <v>402.6756056045592</v>
       </c>
     </row>
     <row r="11">
@@ -5032,25 +5032,25 @@
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>598.13</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L11" t="n">
-        <v>1151.54</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M11" t="n">
-        <v>1662.388828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N11" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5093,13 +5093,13 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D12" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E12" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F12" t="n">
-        <v>461.5662247731743</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G12" t="n">
         <v>380.2433203903244</v>
@@ -5272,16 +5272,16 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1542.849113037656</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>1797.400904947332</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N14" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O14" t="n">
         <v>1797.400904947332</v>
@@ -5293,7 +5293,7 @@
         <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S14" t="n">
         <v>2085.68327354774</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>409.4673863086053</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
         <v>44.72</v>
@@ -5372,28 +5372,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U15" t="n">
-        <v>713.1992034391076</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V15" t="n">
-        <v>648.0369133466629</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W15" t="n">
-        <v>564.8317184882503</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>494.2632948060406</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>444.3729990826726</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5457,22 +5457,22 @@
         <v>44.72</v>
       </c>
       <c r="T16" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U16" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V16" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W16" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X16" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y16" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="17">
@@ -5482,46 +5482,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>690.5809049473327</v>
+        <v>44.72</v>
       </c>
       <c r="L17" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="M17" t="n">
+        <v>555.568828728935</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1108.978828728935</v>
+      </c>
+      <c r="O17" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1243.990904947333</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1797.400904947332</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>1797.400904947332</v>
@@ -5530,28 +5530,28 @@
         <v>2236</v>
       </c>
       <c r="R17" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5570,13 +5570,13 @@
         <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>115.4327932358888</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H18" t="n">
         <v>44.72</v>
@@ -5640,31 +5640,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F19" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G19" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H19" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I19" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J19" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K19" t="n">
         <v>1921.561060958496</v>
@@ -5694,22 +5694,22 @@
         <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>64.92117127106526</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L20" t="n">
-        <v>618.3311712710653</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M20" t="n">
-        <v>1129.18</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N20" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C21" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D21" t="n">
         <v>44.72</v>
@@ -5846,28 +5846,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V21" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W21" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X21" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y21" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="22">
@@ -5931,16 +5931,16 @@
         <v>44.72</v>
       </c>
       <c r="T22" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U22" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V22" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W22" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X22" t="n">
         <v>745.8791912947012</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5995,7 +5995,7 @@
         <v>1500.287941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6019,13 +6019,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G24" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H24" t="n">
         <v>44.72</v>
@@ -6083,28 +6083,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="25">
@@ -6114,31 +6114,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H25" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J25" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K25" t="n">
         <v>1921.561060958496</v>
@@ -6217,19 +6217,19 @@
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>733.1420762183976</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M26" t="n">
-        <v>1243.990904947333</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N26" t="n">
-        <v>1797.400904947332</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O26" t="n">
         <v>1797.400904947332</v>
@@ -6272,22 +6272,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>472.7782575464261</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H27" t="n">
         <v>44.72</v>
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C29" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E29" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F29" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6466,7 +6466,7 @@
         <v>436.0291130376558</v>
       </c>
       <c r="N29" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376557</v>
       </c>
       <c r="O29" t="n">
         <v>1243.990904947333</v>
@@ -6478,28 +6478,28 @@
         <v>2236</v>
       </c>
       <c r="R29" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S29" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T29" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U29" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V29" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W29" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X29" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y29" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="30">
@@ -6509,19 +6509,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F30" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S30" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T30" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U30" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V30" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W30" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X30" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="31">
@@ -6588,16 +6588,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C31" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D31" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E31" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F31" t="n">
         <v>1153.55685638681</v>
@@ -6642,22 +6642,22 @@
         <v>44.72</v>
       </c>
       <c r="T31" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U31" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X31" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y31" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="32">
@@ -6682,28 +6682,28 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>575.7700000000003</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>575.7700000000003</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>575.7700000000003</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1129.18</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
         <v>1682.59</v>
@@ -6791,10 +6791,10 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R33" t="n">
-        <v>937.5750872192207</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S33" t="n">
         <v>466.2983195781991</v>
@@ -6879,10 +6879,10 @@
         <v>44.72</v>
       </c>
       <c r="T34" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U34" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V34" t="n">
         <v>521.9574820108303</v>
@@ -6904,19 +6904,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
         <v>103.3156148520479</v>
@@ -6934,46 +6934,46 @@
         <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
+        <v>989.4391130376558</v>
+      </c>
+      <c r="M35" t="n">
+        <v>989.4391130376558</v>
+      </c>
+      <c r="N35" t="n">
         <v>1542.849113037656</v>
       </c>
-      <c r="M35" t="n">
-        <v>1542.849113037656</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1682.59</v>
-      </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>275.2516144816847</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D36" t="n">
         <v>264.0395817084329</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
         <v>1010.366979583462</v>
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
@@ -7168,10 +7168,10 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>618.3311712710652</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L38" t="n">
-        <v>1171.741171271065</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M38" t="n">
         <v>1682.59</v>
@@ -7189,28 +7189,28 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7223,22 +7223,22 @@
         <v>472.7782575464261</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0308712378207</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D39" t="n">
-        <v>108.0308712378207</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E39" t="n">
-        <v>108.0308712378207</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F39" t="n">
-        <v>108.0308712378207</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G39" t="n">
-        <v>108.0308712378207</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7353,10 +7353,10 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
         <v>521.9574820108303</v>
@@ -7378,46 +7378,46 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="M41" t="n">
-        <v>1500.287941766591</v>
+        <v>555.568828728935</v>
       </c>
       <c r="N41" t="n">
-        <v>1797.400904947332</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P41" t="n">
         <v>1797.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>391.4553531635761</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E42" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F42" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G42" t="n">
         <v>380.2433203903244</v>
@@ -7508,25 +7508,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>801.8216399685234</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>745.9047054053782</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>695.1871702940784</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>630.0248802016338</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>546.8196853432211</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>476.2512616610114</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>426.3609659376434</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L44" t="n">
-        <v>598.13</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M44" t="n">
-        <v>1108.978828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>384.9618669904511</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>913.0695679010663</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>795.3281537953983</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>739.4112192322531</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>688.6936841209533</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>623.5313940285087</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>540.3261991700961</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>469.7577754878864</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.1485167851398</v>
+        <v>419.8674797645184</v>
       </c>
     </row>
     <row r="46">
@@ -7791,10 +7791,10 @@
         <v>1265.174204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J46" t="n">
         <v>1860.696627021627</v>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7976,13 +7976,13 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>846.6934025142796</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>369.7315044851259</v>
       </c>
       <c r="Q2" t="n">
         <v>172.8226843274854</v>
@@ -8204,25 +8204,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444403</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423192</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>385.2870600406827</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q5" t="n">
-        <v>557.8226843274865</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8447,19 +8447,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423201</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698366</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>439.6923140185316</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>557.8226843274865</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L11" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,19 +8915,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>801.3851497733039</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>477.2489580698352</v>
+        <v>777.3630622928068</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>128.4277587171436</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>206.6237041381304</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>20.40522350612653</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>777.3630622928066</v>
       </c>
       <c r="O20" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9638,10 +9638,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>300.4011642636528</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,22 +9860,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
         <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>327.370891705079</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
@@ -10109,10 +10109,10 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N29" t="n">
-        <v>734.371980200822</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>327.3708917050792</v>
       </c>
       <c r="P29" t="n">
         <v>559.2870600406815</v>
@@ -10334,22 +10334,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>536.4141414141418</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>629.2478695740924</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P32" t="n">
         <v>559.2870600406815</v>
@@ -10577,22 +10577,22 @@
         <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>618.4013691429103</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>327.370891705079</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,13 +10811,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>184.14349316506</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,13 +11057,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>777.3630622928066</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>206.6237041381304</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
@@ -11297,13 +11297,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>20.69228354680773</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22715,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.59117064605573</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.591170646055978</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646052603</v>
+        <v>1.591170646054422</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -26311,7 +26311,7 @@
         <v>1416799.170374169</v>
       </c>
       <c r="P2" t="n">
-        <v>1416799.17037417</v>
+        <v>1416799.170374169</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>653286.4838672174</v>
+        <v>651770.6281789016</v>
       </c>
       <c r="C6" t="n">
-        <v>790864.4640010312</v>
+        <v>789348.6083127154</v>
       </c>
       <c r="D6" t="n">
-        <v>792925.2359133473</v>
+        <v>791409.3802250315</v>
       </c>
       <c r="E6" t="n">
-        <v>469045.7671476343</v>
+        <v>467303.9173345267</v>
       </c>
       <c r="F6" t="n">
-        <v>812236.6624931385</v>
+        <v>810494.8126800307</v>
       </c>
       <c r="G6" t="n">
-        <v>814182.2389613241</v>
+        <v>812440.3891482162</v>
       </c>
       <c r="H6" t="n">
-        <v>816130.5157786253</v>
+        <v>814388.6659655176</v>
       </c>
       <c r="I6" t="n">
-        <v>818081.5124219855</v>
+        <v>816339.6626088779</v>
       </c>
       <c r="J6" t="n">
-        <v>404515.2486236106</v>
+        <v>402773.398810503</v>
       </c>
       <c r="K6" t="n">
-        <v>821991.7443758305</v>
+        <v>820249.8945627226</v>
       </c>
       <c r="L6" t="n">
-        <v>823951.0199360895</v>
+        <v>822209.1701229822</v>
       </c>
       <c r="M6" t="n">
-        <v>764665.0958320688</v>
+        <v>762923.2460189612</v>
       </c>
       <c r="N6" t="n">
-        <v>827877.9928669222</v>
+        <v>826136.1430538145</v>
       </c>
       <c r="O6" t="n">
-        <v>549845.7321246604</v>
+        <v>548103.8823115525</v>
       </c>
       <c r="P6" t="n">
-        <v>831816.3349756709</v>
+        <v>830074.4851625629</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27112,10 +27112,10 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,25 +27560,25 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>213.3372327421372</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>81.5639999646113</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>124.5380220625381</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
       </c>
       <c r="W3" t="n">
+        <v>47.37314290982852</v>
+      </c>
+      <c r="X3" t="n">
         <v>400</v>
-      </c>
-      <c r="X3" t="n">
-        <v>34.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27597,16 +27597,16 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>293.3928935650185</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27615,7 +27615,7 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>172.4446636080681</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27673,7 +27673,7 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27831,16 +27831,16 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D7" t="n">
         <v>400</v>
-      </c>
-      <c r="D7" t="n">
-        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>124.021267325552</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>338.7529107212323</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,10 +27882,10 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>272.9308447084231</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>34.24094591625948</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28004,10 +28004,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28071,28 +28071,28 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>380.4097262080851</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>336.9137329713697</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28229,7 +28229,7 @@
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>267.4280115586812</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
@@ -28238,7 +28238,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>245.2298605360059</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -28429,10 +28429,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28463,7 +28463,7 @@
         <v>350</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
@@ -28508,16 +28508,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="S15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>350</v>
       </c>
       <c r="U15" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -28539,61 +28539,61 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>350</v>
+      </c>
+      <c r="C16" t="n">
+        <v>350</v>
+      </c>
+      <c r="D16" t="n">
+        <v>350</v>
+      </c>
+      <c r="E16" t="n">
+        <v>350</v>
+      </c>
+      <c r="F16" t="n">
+        <v>350</v>
+      </c>
+      <c r="G16" t="n">
+        <v>350</v>
+      </c>
+      <c r="H16" t="n">
+        <v>350</v>
+      </c>
+      <c r="I16" t="n">
+        <v>350</v>
+      </c>
+      <c r="J16" t="n">
+        <v>350</v>
+      </c>
+      <c r="K16" t="n">
+        <v>350</v>
+      </c>
+      <c r="L16" t="n">
+        <v>350</v>
+      </c>
+      <c r="M16" t="n">
+        <v>350</v>
+      </c>
+      <c r="N16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O16" t="n">
+        <v>350</v>
+      </c>
+      <c r="P16" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>350</v>
+      </c>
+      <c r="R16" t="n">
+        <v>350</v>
+      </c>
+      <c r="S16" t="n">
+        <v>350</v>
+      </c>
+      <c r="T16" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="C16" t="n">
-        <v>350</v>
-      </c>
-      <c r="D16" t="n">
-        <v>350</v>
-      </c>
-      <c r="E16" t="n">
-        <v>350</v>
-      </c>
-      <c r="F16" t="n">
-        <v>350</v>
-      </c>
-      <c r="G16" t="n">
-        <v>350</v>
-      </c>
-      <c r="H16" t="n">
-        <v>350</v>
-      </c>
-      <c r="I16" t="n">
-        <v>350</v>
-      </c>
-      <c r="J16" t="n">
-        <v>350</v>
-      </c>
-      <c r="K16" t="n">
-        <v>350</v>
-      </c>
-      <c r="L16" t="n">
-        <v>350</v>
-      </c>
-      <c r="M16" t="n">
-        <v>350</v>
-      </c>
-      <c r="N16" t="n">
-        <v>350</v>
-      </c>
-      <c r="O16" t="n">
-        <v>350</v>
-      </c>
-      <c r="P16" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>350</v>
-      </c>
-      <c r="R16" t="n">
-        <v>350</v>
-      </c>
-      <c r="S16" t="n">
-        <v>350</v>
-      </c>
-      <c r="T16" t="n">
-        <v>350</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
         <v>350</v>
@@ -28706,16 +28706,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>269.6305770343469</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H18" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>217.1263858913485</v>
@@ -28803,7 +28803,7 @@
         <v>350</v>
       </c>
       <c r="K19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L19" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28940,7 +28940,7 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -28982,10 +28982,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T21" t="n">
         <v>350</v>
@@ -29000,7 +29000,7 @@
         <v>350</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y21" t="n">
         <v>350</v>
@@ -29067,7 +29067,7 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29079,7 +29079,7 @@
         <v>350</v>
       </c>
       <c r="X22" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y22" t="n">
         <v>350</v>
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29155,7 +29155,7 @@
         <v>350</v>
       </c>
       <c r="W23" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X23" t="n">
         <v>350</v>
@@ -29186,10 +29186,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>245.2298605360059</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29219,13 +29219,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="U24" t="n">
         <v>350</v>
@@ -29250,7 +29250,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C25" t="n">
         <v>350</v>
@@ -29277,7 +29277,7 @@
         <v>350</v>
       </c>
       <c r="K25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L25" t="n">
         <v>350</v>
@@ -29408,10 +29408,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="C27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>347.9376868977026</v>
@@ -29423,10 +29423,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>245.2298605360059</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I27" t="n">
         <v>217.1263858913485</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S29" t="n">
         <v>350</v>
@@ -29660,7 +29660,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>263.0617733495849</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
         <v>332.1680871864211</v>
@@ -29693,10 +29693,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T30" t="n">
         <v>350</v>
@@ -29714,7 +29714,7 @@
         <v>350</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31">
@@ -29736,7 +29736,7 @@
         <v>350</v>
       </c>
       <c r="F31" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G31" t="n">
         <v>350</v>
@@ -29778,7 +29778,7 @@
         <v>350</v>
       </c>
       <c r="T31" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U31" t="n">
         <v>350</v>
@@ -29818,13 +29818,13 @@
         <v>350</v>
       </c>
       <c r="G32" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29927,13 +29927,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>287.3222374745576</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T33" t="n">
         <v>350</v>
@@ -30015,13 +30015,13 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
       </c>
       <c r="V34" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W34" t="n">
         <v>350</v>
@@ -30055,7 +30055,7 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30119,13 +30119,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="C36" t="n">
         <v>350</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>152.3863102636086</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30198,13 +30198,13 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>350</v>
+      </c>
+      <c r="C37" t="n">
+        <v>350</v>
+      </c>
+      <c r="D37" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="C37" t="n">
-        <v>350</v>
-      </c>
-      <c r="D37" t="n">
-        <v>350</v>
       </c>
       <c r="E37" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30359,7 +30359,7 @@
         <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>154.448623365906</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30374,10 +30374,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>269.4903246609786</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30489,13 +30489,13 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
+        <v>350</v>
+      </c>
+      <c r="U40" t="n">
+        <v>350</v>
+      </c>
+      <c r="V40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U40" t="n">
-        <v>350</v>
-      </c>
-      <c r="V40" t="n">
-        <v>350</v>
       </c>
       <c r="W40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30608,7 +30608,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -30644,7 +30644,7 @@
         <v>350</v>
       </c>
       <c r="S42" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30845,7 +30845,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>332.1680871864211</v>
@@ -30878,7 +30878,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30899,7 +30899,7 @@
         <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46">
@@ -30927,13 +30927,13 @@
         <v>350</v>
       </c>
       <c r="H46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="I46" t="n">
         <v>350</v>
       </c>
       <c r="J46" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34755,13 +34755,13 @@
         <v>385</v>
       </c>
       <c r="N2" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="O2" t="n">
         <v>385</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34883,16 +34883,16 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>48.34902072348844</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34901,7 +34901,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>137.1757147721603</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,25 +34983,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444403</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385.0000000000019</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="P5" t="n">
-        <v>385.0000000000013</v>
+        <v>385</v>
       </c>
       <c r="Q5" t="n">
-        <v>385.0000000000011</v>
+        <v>385</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,16 +35117,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
@@ -35138,10 +35138,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>88.7523184896442</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>50.23213692008925</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,10 +35168,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
@@ -35226,19 +35226,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>385.0000000000028</v>
+        <v>385</v>
       </c>
       <c r="N8" t="n">
-        <v>385.0000000000014</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>369.4444444444392</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385.0000000000011</v>
+        <v>385</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35357,28 +35357,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>94.87350815252962</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>110.54092313266</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L11" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35694,19 +35694,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N14" t="n">
+        <v>300.1141042229716</v>
+      </c>
+      <c r="O14" t="n">
         <v>559</v>
-      </c>
-      <c r="L14" t="n">
-        <v>559</v>
-      </c>
-      <c r="M14" t="n">
-        <v>257.1230221309866</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35825,7 +35825,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C16" t="n">
         <v>77.27475335195533</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36089,7 +36089,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K19" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>20.40522350612653</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="O20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36365,7 +36365,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X22" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y22" t="n">
         <v>62.53464715053764</v>
@@ -36417,10 +36417,10 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>300.1141042229714</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36536,7 +36536,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C25" t="n">
         <v>77.27475335195533</v>
@@ -36563,7 +36563,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K25" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36639,22 +36639,22 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
         <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>559</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36888,10 +36888,10 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>257.1230221309867</v>
+        <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>257.1230221309868</v>
       </c>
       <c r="P29" t="n">
         <v>559</v>
@@ -37022,7 +37022,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F31" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G31" t="n">
         <v>104.95612715847</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U31" t="n">
         <v>199.0416087255421</v>
@@ -37113,22 +37113,22 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>536.4141414141418</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P32" t="n">
         <v>559</v>
@@ -37301,13 +37301,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V34" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W34" t="n">
         <v>123.6271901612903</v>
@@ -37356,22 +37356,22 @@
         <v>559</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>559</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>141.1524110730751</v>
-      </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37484,13 +37484,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C37" t="n">
         <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E37" t="n">
         <v>69.01909516304346</v>
@@ -37590,13 +37590,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>184.14349316506</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
@@ -37775,13 +37775,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V40" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W40" t="n">
         <v>123.6271901612903</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37836,13 +37836,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
@@ -38076,13 +38076,13 @@
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,13 +38213,13 @@
         <v>104.95612715847</v>
       </c>
       <c r="H46" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I46" t="n">
         <v>173.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K46" t="n">
         <v>61.47922619885696</v>
